--- a/data/trans_bre/P15A-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P15A-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 2,57</t>
+          <t>-3,83; 2,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 1,08</t>
+          <t>-4,53; 1,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 3,86</t>
+          <t>-1,65; 3,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 3,93</t>
+          <t>-0,62; 4,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-77,55; 138,4</t>
+          <t>-79,16; 101,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-82,81; 61,14</t>
+          <t>-83,34; 66,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-52,93; 470,37</t>
+          <t>-57,4; 443,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-18,38; 285,28</t>
+          <t>-21,29; 300,34</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,63</t>
+          <t>-1,47; 1,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 0,84</t>
+          <t>-2,47; 0,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 0,75</t>
+          <t>-1,85; 0,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 2,64</t>
+          <t>-1,62; 2,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,14; 207,44</t>
+          <t>-64,54; 233,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-77,6; 84,19</t>
+          <t>-79,6; 90,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-86,72; 203,86</t>
+          <t>-88,37; 174,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,41; 219,79</t>
+          <t>-45,02; 277,87</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,91; -2,02</t>
+          <t>-8,01; -1,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 3,76</t>
+          <t>-2,66; 3,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 0,0</t>
+          <t>-5,02; 0,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 2,44</t>
+          <t>-1,04; 2,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-94,11; -29,52</t>
+          <t>-94,92; -31,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-47,66; 126,71</t>
+          <t>-45,8; 130,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-86,97; 17,65</t>
+          <t>-85,68; 16,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-50,74; 275,23</t>
+          <t>-41,89; 291,26</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 0,25</t>
+          <t>-5,02; 0,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 0,48</t>
+          <t>-4,94; 0,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 3,59</t>
+          <t>-2,74; 3,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 1,43</t>
+          <t>-5,12; 1,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-75,58; 16,95</t>
+          <t>-79,0; 11,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-83,94; 47,62</t>
+          <t>-84,06; 41,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-52,54; 115,31</t>
+          <t>-45,69; 151,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-94,18; 293,04</t>
+          <t>-91,75; 349,26</t>
         </is>
       </c>
     </row>
@@ -1060,37 +1060,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 4,19</t>
+          <t>-3,92; 3,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 4,41</t>
+          <t>-2,9; 4,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 1,58</t>
+          <t>-3,87; 1,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 0,11</t>
+          <t>-3,52; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-69,52; 219,83</t>
+          <t>-73,5; 223,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-60,69; 246,47</t>
+          <t>-59,71; 245,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-90,2; 186,71</t>
+          <t>-100,0; 154,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 3,69</t>
+          <t>-2,44; 3,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,24; 7,17</t>
+          <t>0,0; 7,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 8,16</t>
+          <t>-1,02; 8,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 4,44</t>
+          <t>-1,25; 4,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-62,1; 220,34</t>
+          <t>-56,17; 237,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,71; 598,7</t>
+          <t>-21,73; 612,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,88; 202,02</t>
+          <t>-14,2; 216,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-26,69; 182,28</t>
+          <t>-29,54; 209,73</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 0,44</t>
+          <t>-3,68; 0,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,27</t>
+          <t>-2,53; 1,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,73</t>
+          <t>-1,64; 0,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 1,87</t>
+          <t>-1,64; 1,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-67,58; 13,46</t>
+          <t>-65,6; 22,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-55,72; 54,49</t>
+          <t>-58,71; 39,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-88,79; 161,69</t>
+          <t>-84,16; 170,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-56,4; 130,83</t>
+          <t>-57,84; 126,78</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 1,86</t>
+          <t>-2,09; 1,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,96</t>
+          <t>-0,74; 1,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 0,77</t>
+          <t>-2,01; 0,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,85</t>
+          <t>-1,21; 1,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-42,36; 74,0</t>
+          <t>-45,37; 66,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-39,56; 319,5</t>
+          <t>-46,64; 286,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-64,54; 53,51</t>
+          <t>-65,79; 62,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-50,94; 216,06</t>
+          <t>-50,31; 245,2</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,88; -0,16</t>
+          <t>-1,89; 0,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,74</t>
+          <t>-0,9; 0,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,68</t>
+          <t>-0,97; 0,58</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,24</t>
+          <t>-0,42; 1,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-44,11; -4,51</t>
+          <t>-44,44; -0,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-28,67; 30,62</t>
+          <t>-27,6; 27,58</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-30,78; 29,27</t>
+          <t>-33,54; 25,8</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-17,97; 72,31</t>
+          <t>-15,6; 69,62</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P15A-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P15A-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,73</t>
+          <t>1,46</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>53,62%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 2,04</t>
+          <t>-3,61; 2,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 1,41</t>
+          <t>-4,62; 1,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 3,93</t>
+          <t>-1,54; 4,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 4,25</t>
+          <t>-0,89; 3,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-79,16; 101,35</t>
+          <t>-76,48; 137,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-83,34; 66,73</t>
+          <t>-82,38; 57,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-57,4; 443,81</t>
+          <t>-57,74; 356,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-21,29; 300,34</t>
+          <t>-30,36; 222,87</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,8</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>35,57%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 1,89</t>
+          <t>-1,55; 1,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,89</t>
+          <t>-2,58; 1,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 0,77</t>
+          <t>-1,87; 0,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 2,87</t>
+          <t>-1,34; 2,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,54; 233,24</t>
+          <t>-66,6; 278,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-79,6; 90,74</t>
+          <t>-79,08; 103,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-88,37; 174,7</t>
+          <t>-90,95; 167,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,02; 277,87</t>
+          <t>-38,49; 296,0</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,01; -1,66</t>
+          <t>-7,68; -1,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 3,91</t>
+          <t>-3,33; 3,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 0,07</t>
+          <t>-5,21; 0,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 2,62</t>
+          <t>-1,89; 2,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-94,92; -31,26</t>
+          <t>-94,35; -31,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-45,8; 130,97</t>
+          <t>-53,23; 109,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-85,68; 16,32</t>
+          <t>-85,79; 25,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-41,89; 291,26</t>
+          <t>-53,59; 202,39</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,89</t>
+          <t>-1,01</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-38,53%</t>
+          <t>-36,78%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 0,35</t>
+          <t>-5,19; 0,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 0,46</t>
+          <t>-4,84; 0,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 3,98</t>
+          <t>-3,02; 3,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 1,41</t>
+          <t>-4,37; 2,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-79,0; 11,92</t>
+          <t>-78,87; 22,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-84,06; 41,71</t>
+          <t>-85,22; 19,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-45,69; 151,38</t>
+          <t>-50,28; 127,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-91,75; 349,26</t>
+          <t>-88,14; 410,79</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,97</t>
+          <t>-0,95</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-78,94%</t>
+          <t>-80,41%</t>
         </is>
       </c>
     </row>
@@ -1060,37 +1060,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 3,98</t>
+          <t>-3,56; 3,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 4,25</t>
+          <t>-2,71; 4,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 1,49</t>
+          <t>-3,92; 1,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 0,0</t>
+          <t>-3,26; 0,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-73,5; 223,96</t>
+          <t>-70,59; 261,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-59,71; 245,55</t>
+          <t>-57,12; 256,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 154,88</t>
+          <t>-100,0; 220,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,66</t>
+          <t>1,93</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>56,9%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 3,77</t>
+          <t>-2,76; 4,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,16</t>
+          <t>0,25; 7,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 8,38</t>
+          <t>-1,13; 7,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 4,47</t>
+          <t>-0,85; 4,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-56,17; 237,1</t>
+          <t>-60,56; 239,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-21,73; 612,58</t>
+          <t>-20,46; 665,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 216,18</t>
+          <t>-16,23; 204,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-29,54; 209,73</t>
+          <t>-21,28; 198,18</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,8</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>35,97%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 0,55</t>
+          <t>-3,73; 0,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 1,09</t>
+          <t>-2,62; 1,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,78</t>
+          <t>-1,7; 0,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 1,87</t>
+          <t>-0,95; 2,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-65,6; 22,13</t>
+          <t>-64,01; 18,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-58,71; 39,71</t>
+          <t>-58,01; 42,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-84,16; 170,28</t>
+          <t>-86,57; 134,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-57,84; 126,78</t>
+          <t>-32,21; 156,63</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>-0,29</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>-13,41%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 1,72</t>
+          <t>-1,87; 1,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,84</t>
+          <t>-0,66; 1,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,92</t>
+          <t>-1,89; 0,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,79</t>
+          <t>-2,01; 1,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-45,37; 66,01</t>
+          <t>-44,24; 66,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-46,64; 286,9</t>
+          <t>-47,87; 290,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-65,79; 62,02</t>
+          <t>-62,78; 53,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-50,31; 245,2</t>
+          <t>-61,35; 103,4</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,01</t>
+          <t>-1,83; -0,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,7</t>
+          <t>-0,96; 0,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 0,58</t>
+          <t>-0,9; 0,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 1,18</t>
+          <t>-0,41; 1,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-44,44; -0,01</t>
+          <t>-43,63; -4,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-27,6; 27,58</t>
+          <t>-28,15; 26,38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-33,54; 25,8</t>
+          <t>-30,35; 30,67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 69,62</t>
+          <t>-14,28; 62,47</t>
         </is>
       </c>
     </row>
